--- a/artfynd/A 41640-2023 artfynd.xlsx
+++ b/artfynd/A 41640-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 41640-2023 artfynd.xlsx
+++ b/artfynd/A 41640-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>86511826</v>
+        <v>86511777</v>
       </c>
       <c r="B2" t="n">
-        <v>96362</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111389</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219865</v>
+        <v>219711</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Johannesnycklar</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Orchis militaris</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -715,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>608570.6710858089</v>
+        <v>608264</v>
       </c>
       <c r="R2" t="n">
-        <v>6297342.518675208</v>
+        <v>6297283</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,21 +743,11 @@
           <t>2020-06-25</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-06-25</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -774,7 +759,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>fuktig betesmark</t>
+          <t>granskog med hassel</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -788,7 +773,643 @@
           <t>Tomas Burén</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>86511831</v>
+      </c>
+      <c r="B3" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Störlinge bodar NV, Öl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>608589</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6297302</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Gärdslösa</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2020-06-25</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2020-06-25</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>fuktig betesmark</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Tomas Burén</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Tomas Burén</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>86511826</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99148</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>219865</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Johannesnycklar</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Orchis militaris</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Störlinge bodar NV, Öl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>608571</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6297343</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Gärdslösa</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2020-06-25</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2020-06-25</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>fuktig betesmark</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Tomas Burén</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Tomas Burén</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>86511828</v>
+      </c>
+      <c r="B5" t="n">
+        <v>108115</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220079</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Jordtistel</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Störlinge bodar NV, Öl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>608589</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6297302</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Gärdslösa</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2020-06-25</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2020-06-25</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>fuktig betesmark</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Tomas Burén</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Tomas Burén</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>86511827</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99145</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222118</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Flugblomster</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Ophrys insectifera</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Störlinge bodar NV, Öl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>608589</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6297302</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Gärdslösa</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2020-06-25</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2020-06-25</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>fuktig betesmark</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Tomas Burén</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Tomas Burén</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>86511776</v>
+      </c>
+      <c r="B7" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Störlinge bodar NV, Öl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>608264</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6297283</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Gärdslösa</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2020-06-25</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2020-06-25</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>granskog med hassel</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Tomas Burén</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Tomas Burén</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>86511832</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99029</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>223578</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Äkta ängsnycklar</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dactylorhiza incarnata var. incarnata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Störlinge bodar NV, Öl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>608589</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6297302</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Borgholm</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Gärdslösa</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2020-06-25</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2020-06-25</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>fuktig betesmark</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Tomas Burén</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Tomas Burén</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 41640-2023 artfynd.xlsx
+++ b/artfynd/A 41640-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86511777</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86511831</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86511826</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86511828</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86511827</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1308,6 +1338,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86511776</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1410,8 +1445,22 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86511832</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>